--- a/data/trans_orig/CLASESOCIAL_Hogar_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_Hogar_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social del hogar, recodificación en grupos en 2007</t>
+          <t>Población según la clase social del hogar en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137670</t>
+          <t>140083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183819</t>
+          <t>182340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>383738</t>
+          <t>383163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>437129</t>
+          <t>433187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538232</t>
+          <t>535636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>611895</t>
+          <t>604914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277779</t>
+          <t>281025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>329755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146144</t>
+          <t>147602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191253</t>
+          <t>190718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439153</t>
+          <t>440208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>509893</t>
+          <t>510267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87789</t>
+          <t>87246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>124942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>26600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51012</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>118348</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164666</t>
+          <t>165387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>40245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68659</t>
+          <t>70132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47428</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>72584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109208</t>
+          <t>110216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55166</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85640</t>
+          <t>85839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>26160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51686</t>
+          <t>51053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86778</t>
+          <t>88628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125813</t>
+          <t>127670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166337</t>
+          <t>167231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216035</t>
+          <t>215287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>481484</t>
+          <t>486278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>544418</t>
+          <t>548414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>661201</t>
+          <t>662456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>745789</t>
+          <t>748593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381850</t>
+          <t>383059</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>443529</t>
+          <t>445646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187995</t>
+          <t>187192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241793</t>
+          <t>239267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583595</t>
+          <t>586600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668484</t>
+          <t>672168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125392</t>
+          <t>123937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171010</t>
+          <t>171873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80907</t>
+          <t>80178</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>185790</t>
+          <t>182699</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241445</t>
+          <t>238640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73854</t>
+          <t>74547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111330</t>
+          <t>112348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,49 +1769,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>93446</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>74508</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>112191</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>7,69%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>11,59%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>93446</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>77256</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>114063</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157984</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211557</t>
+          <t>211405</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97920</t>
+          <t>99147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138990</t>
+          <t>141061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>67474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102272</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177806</t>
+          <t>177532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>230501</t>
+          <t>233075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89276</t>
+          <t>91977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128987</t>
+          <t>131006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351538</t>
+          <t>349043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>401070</t>
+          <t>399515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450052</t>
+          <t>450444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>518043</t>
+          <t>520473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214094</t>
+          <t>217932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>266760</t>
+          <t>268201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112448</t>
+          <t>113028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152902</t>
+          <t>152442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344540</t>
+          <t>342233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408959</t>
+          <t>407224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>101870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145696</t>
+          <t>143032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>120380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164642</t>
+          <t>164804</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>72995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112071</t>
+          <t>110877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80113</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116878</t>
+          <t>116785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>164790</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215867</t>
+          <t>215177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96205</t>
+          <t>94830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135197</t>
+          <t>135177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45639</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73843</t>
+          <t>74485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149098</t>
+          <t>146792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199441</t>
+          <t>197507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165644</t>
+          <t>167509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>213404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>484590</t>
+          <t>485063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>546582</t>
+          <t>546813</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>663281</t>
+          <t>660939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>750505</t>
+          <t>747675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249825</t>
+          <t>251233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>306965</t>
+          <t>305461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175583</t>
+          <t>178252</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227749</t>
+          <t>227346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>438786</t>
+          <t>439532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513648</t>
+          <t>514726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>147411</t>
+          <t>146309</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>192467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>34377</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62125</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>189975</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243079</t>
+          <t>247333</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112249</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153532</t>
+          <t>152427</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124398</t>
+          <t>123535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169318</t>
+          <t>168919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249345</t>
+          <t>243695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308501</t>
+          <t>305611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151233</t>
+          <t>150096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197407</t>
+          <t>195982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106136</t>
+          <t>106999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148847</t>
+          <t>148584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271543</t>
+          <t>269361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>331383</t>
+          <t>334769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>605068</t>
+          <t>599812</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>699147</t>
+          <t>697472</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1754126</t>
+          <t>1758722</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1869461</t>
+          <t>1874330</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2390502</t>
+          <t>2386371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2541052</t>
+          <t>2546137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1180579</t>
+          <t>1177587</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1298417</t>
+          <t>1295040</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>671714</t>
+          <t>669763</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>762070</t>
+          <t>761631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1880987</t>
+          <t>1877946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2033894</t>
+          <t>2030559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>502803</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>586888</t>
+          <t>587079</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>144650</t>
+          <t>142595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>195890</t>
+          <t>194139</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>661673</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>757502</t>
+          <t>763155</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>331636</t>
+          <t>332112</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>405546</t>
+          <t>405521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>335700</t>
+          <t>338076</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>407234</t>
+          <t>412182</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>690387</t>
+          <t>689070</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>794725</t>
+          <t>795843</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>434428</t>
+          <t>435160</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>513171</t>
+          <t>516845</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>276827</t>
+          <t>278822</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>345732</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>731355</t>
+          <t>730490</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>836446</t>
+          <t>841847</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social del hogar, recodificación en grupos en 2012</t>
+          <t>Población según la clase social del hogar en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160763</t>
+          <t>159727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206353</t>
+          <t>207417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>395410</t>
+          <t>393353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>447742</t>
+          <t>447089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567397</t>
+          <t>563288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>642517</t>
+          <t>642033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234376</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284539</t>
+          <t>283960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110131</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151373</t>
+          <t>152926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354843</t>
+          <t>353009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425079</t>
+          <t>424194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120663</t>
+          <t>118841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165972</t>
+          <t>162850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72533</t>
+          <t>71507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168679</t>
+          <t>170411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219997</t>
+          <t>223230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78501</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51289</t>
+          <t>48116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77943</t>
+          <t>77279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>119734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49410</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>37690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67369</t>
+          <t>66901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94820</t>
+          <t>95563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136333</t>
+          <t>136591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245364</t>
+          <t>245592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305743</t>
+          <t>305316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>518925</t>
+          <t>521806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>582464</t>
+          <t>585339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>782055</t>
+          <t>783455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>872615</t>
+          <t>874586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317649</t>
+          <t>315405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381146</t>
+          <t>377372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198189</t>
+          <t>197336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249015</t>
+          <t>251768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529613</t>
+          <t>528703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617654</t>
+          <t>612409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144275</t>
+          <t>147408</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195856</t>
+          <t>196755</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>72612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109376</t>
+          <t>109730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>229252</t>
+          <t>230266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>292527</t>
+          <t>296195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84329</t>
+          <t>85280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>126893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73778</t>
+          <t>73071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114268</t>
+          <t>112387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168554</t>
+          <t>170123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227233</t>
+          <t>225611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99324</t>
+          <t>100643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143889</t>
+          <t>144392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>60228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95168</t>
+          <t>97212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165668</t>
+          <t>167471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224834</t>
+          <t>225236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119023</t>
+          <t>119362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163188</t>
+          <t>163297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>376128</t>
+          <t>373854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>432353</t>
+          <t>432267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506448</t>
+          <t>505873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>583937</t>
+          <t>579366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247361</t>
+          <t>249730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>305636</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158215</t>
+          <t>157393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204944</t>
+          <t>207321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420944</t>
+          <t>418300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>496871</t>
+          <t>496519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117146</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162529</t>
+          <t>164875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65407</t>
+          <t>67079</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165643</t>
+          <t>164481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>216746</t>
+          <t>219516</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81074</t>
+          <t>81596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123540</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>58186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>93911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147779</t>
+          <t>149521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200411</t>
+          <t>200872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80281</t>
+          <t>78677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123285</t>
+          <t>120553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>51113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86589</t>
+          <t>86552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141845</t>
+          <t>143659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194429</t>
+          <t>194479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156914</t>
+          <t>155944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>209146</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>462850</t>
+          <t>464884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>528027</t>
+          <t>525901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>634814</t>
+          <t>635740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>715976</t>
+          <t>720619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247972</t>
+          <t>250681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307646</t>
+          <t>307550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202456</t>
+          <t>203445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256192</t>
+          <t>258589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470377</t>
+          <t>463066</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>551061</t>
+          <t>548495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>158164</t>
+          <t>156262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206778</t>
+          <t>204266</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>51775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>216701</t>
+          <t>216332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>273779</t>
+          <t>274647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130437</t>
+          <t>130422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175709</t>
+          <t>179781</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119033</t>
+          <t>120287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>165987</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259180</t>
+          <t>260240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324190</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132867</t>
+          <t>133795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178062</t>
+          <t>177566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100071</t>
+          <t>99257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142966</t>
+          <t>142261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>243850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>309196</t>
+          <t>308130</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>724085</t>
+          <t>730082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>828248</t>
+          <t>831846</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1809739</t>
+          <t>1802337</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1934982</t>
+          <t>1927299</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2565720</t>
+          <t>2566804</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2736049</t>
+          <t>2737270</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1101853</t>
+          <t>1098547</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1217094</t>
+          <t>1213518</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>723472</t>
+          <t>717585</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>829385</t>
+          <t>818227</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1844883</t>
+          <t>1851860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1998264</t>
+          <t>2013927</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>579173</t>
+          <t>583397</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>675413</t>
+          <t>675684</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>229022</t>
+          <t>231269</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>292139</t>
+          <t>292526</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>836726</t>
+          <t>831079</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>952772</t>
+          <t>953851</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>377679</t>
+          <t>379269</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>463456</t>
+          <t>461909</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>300224</t>
+          <t>301749</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>378745</t>
+          <t>374524</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>700590</t>
+          <t>702236</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>808332</t>
+          <t>812977</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>398133</t>
+          <t>397051</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>480582</t>
+          <t>480075</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>279334</t>
+          <t>280093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>347841</t>
+          <t>353175</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>699295</t>
+          <t>699548</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>805722</t>
+          <t>808753</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social del hogar, recodificación en grupos en 2016</t>
+          <t>Población según la clase social del hogar en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>243367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295910</t>
+          <t>293166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387279</t>
+          <t>387222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>439294</t>
+          <t>437030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>644302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>715178</t>
+          <t>721227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196167</t>
+          <t>196396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246105</t>
+          <t>244489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138629</t>
+          <t>138175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180555</t>
+          <t>182930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350557</t>
+          <t>346062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409116</t>
+          <t>414294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77445</t>
+          <t>76326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115131</t>
+          <t>113207</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>38819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>102578</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146082</t>
+          <t>146833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>56648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91373</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67364</t>
+          <t>65638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,47 +8484,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>39150</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28478</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53932</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39150</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27834</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>52537</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73103</t>
+          <t>75505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110430</t>
+          <t>111742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265254</t>
+          <t>265106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324318</t>
+          <t>326214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>507818</t>
+          <t>509916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>575199</t>
+          <t>573783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>788747</t>
+          <t>789881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>879168</t>
+          <t>877637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322944</t>
+          <t>319392</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384187</t>
+          <t>383952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227143</t>
+          <t>226309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283630</t>
+          <t>282706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567860</t>
+          <t>560758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648696</t>
+          <t>647795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131270</t>
+          <t>130454</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176166</t>
+          <t>179711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>42976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74970</t>
+          <t>75379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>183177</t>
+          <t>185956</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237145</t>
+          <t>241627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89254</t>
+          <t>91264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131827</t>
+          <t>131577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75485</t>
+          <t>77073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114405</t>
+          <t>115391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174701</t>
+          <t>177102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231690</t>
+          <t>233467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95393</t>
+          <t>92783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134836</t>
+          <t>135804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73122</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112220</t>
+          <t>112396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179021</t>
+          <t>177648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235577</t>
+          <t>232609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147822</t>
+          <t>145416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192645</t>
+          <t>192077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>352236</t>
+          <t>354018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409330</t>
+          <t>408053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>511580</t>
+          <t>510846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>584640</t>
+          <t>587238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279140</t>
+          <t>279545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334506</t>
+          <t>335572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174094</t>
+          <t>173102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>223002</t>
+          <t>220470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>471968</t>
+          <t>465806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540860</t>
+          <t>542218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101370</t>
+          <t>99705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140757</t>
+          <t>140716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49888</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133638</t>
+          <t>133333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180991</t>
+          <t>181860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61543</t>
+          <t>60297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>94733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79938</t>
+          <t>79675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117069</t>
+          <t>114852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198270</t>
+          <t>198620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>61750</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101085</t>
+          <t>99308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>55437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>87753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129650</t>
+          <t>129400</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176325</t>
+          <t>175844</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152213</t>
+          <t>153818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200584</t>
+          <t>201195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>451983</t>
+          <t>449567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>521833</t>
+          <t>518538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>619009</t>
+          <t>619369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>702029</t>
+          <t>709759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243519</t>
+          <t>242820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>299036</t>
+          <t>298297</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190603</t>
+          <t>189008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244914</t>
+          <t>242727</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>448282</t>
+          <t>447045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>523224</t>
+          <t>525144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133627</t>
+          <t>131779</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177841</t>
+          <t>177168</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172832</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>226571</t>
+          <t>225731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129922</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174056</t>
+          <t>173460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128343</t>
+          <t>127927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174436</t>
+          <t>174296</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269209</t>
+          <t>270121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>334853</t>
+          <t>340120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161582</t>
+          <t>161774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210635</t>
+          <t>208507</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123281</t>
+          <t>123402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>169652</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>294395</t>
+          <t>294637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>361754</t>
+          <t>362048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>855807</t>
+          <t>852444</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>962439</t>
+          <t>961037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1757215</t>
+          <t>1758303</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1879784</t>
+          <t>1875817</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2649388</t>
+          <t>2642453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2805099</t>
+          <t>2803331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1091863</t>
+          <t>1099546</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1206793</t>
+          <t>1207276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>774825</t>
+          <t>775947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>878440</t>
+          <t>877477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1901701</t>
+          <t>1899822</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2050236</t>
+          <t>2053917</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>482663</t>
+          <t>479151</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>565255</t>
+          <t>565326</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>140483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>194474</t>
+          <t>194903</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>636425</t>
+          <t>638827</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>739625</t>
+          <t>737815</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>341542</t>
+          <t>341358</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>419538</t>
+          <t>414341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>334025</t>
+          <t>334751</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>412343</t>
+          <t>407293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>697429</t>
+          <t>702156</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>805317</t>
+          <t>803740</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>387533</t>
+          <t>391180</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>468945</t>
+          <t>470225</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>314317</t>
+          <t>312589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>384354</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>727988</t>
+          <t>718318</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>836105</t>
+          <t>831543</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social del hogar, recodificación en grupos en 2023</t>
+          <t>Población según la clase social del hogar en 2023 (tasa de respuesta: 97,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125008</t>
+          <t>123318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171515</t>
+          <t>169908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189247</t>
+          <t>189109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226942</t>
+          <t>226411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>323631</t>
+          <t>321955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381282</t>
+          <t>381448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247422</t>
+          <t>246781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300527</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222760</t>
+          <t>221578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260727</t>
+          <t>262774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483621</t>
+          <t>483828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549029</t>
+          <t>553209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76411</t>
+          <t>77161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118745</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63191</t>
+          <t>64116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90952</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>149975</t>
+          <t>147259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200575</t>
+          <t>201267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>67260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83552</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>102719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140485</t>
+          <t>141504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47069</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>78404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57595</t>
+          <t>58171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>83494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112372</t>
+          <t>111384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153271</t>
+          <t>151203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66468</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191966</t>
+          <t>194774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205157</t>
+          <t>206156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248776</t>
+          <t>249472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241807</t>
+          <t>240425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>430795</t>
+          <t>431207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176032</t>
+          <t>197068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463431</t>
+          <t>465226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303206</t>
+          <t>301995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>352122</t>
+          <t>350490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>460742</t>
+          <t>454135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>787085</t>
+          <t>783483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172913</t>
+          <t>174108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>786588</t>
+          <t>751884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81611</t>
+          <t>82625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>113358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266952</t>
+          <t>268093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1007554</t>
+          <t>1070521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>71903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183648</t>
+          <t>186846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150865</t>
+          <t>150271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171455</t>
+          <t>170297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311016</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73220</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199036</t>
+          <t>199730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137120</t>
+          <t>135714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178035</t>
+          <t>175285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203235</t>
+          <t>204806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>352736</t>
+          <t>357757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73133</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115861</t>
+          <t>116027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92512</t>
+          <t>94213</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265594</t>
+          <t>269996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>193455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362654</t>
+          <t>363561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203634</t>
+          <t>202079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>261218</t>
+          <t>257980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127621</t>
+          <t>118175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319807</t>
+          <t>319721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307906</t>
+          <t>305947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>556773</t>
+          <t>553725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96678</t>
+          <t>98957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143199</t>
+          <t>145549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94973</t>
+          <t>95907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120261</t>
+          <t>120485</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228547</t>
+          <t>228415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98841</t>
+          <t>98696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>143539</t>
+          <t>145417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122167</t>
+          <t>121649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>582410</t>
+          <t>611569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>242221</t>
+          <t>243080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>870282</t>
+          <t>838746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113034</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163317</t>
+          <t>162499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62626</t>
+          <t>58279</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167112</t>
+          <t>167492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159084</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310404</t>
+          <t>310197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94424</t>
+          <t>91596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140457</t>
+          <t>141432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193177</t>
+          <t>192971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>419375</t>
+          <t>439460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302208</t>
+          <t>298749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>588302</t>
+          <t>585138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230017</t>
+          <t>228487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>290025</t>
+          <t>291089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226650</t>
+          <t>231336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316278</t>
+          <t>314431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472874</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583492</t>
+          <t>590383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>105085</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150455</t>
+          <t>150446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85816</t>
+          <t>85893</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128361</t>
+          <t>128384</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>201504</t>
+          <t>198545</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263983</t>
+          <t>267306</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157946</t>
+          <t>157250</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209323</t>
+          <t>208682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149172</t>
+          <t>146193</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206618</t>
+          <t>206665</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322818</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>400746</t>
+          <t>402939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209784</t>
+          <t>208554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>266530</t>
+          <t>266073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188799</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>261719</t>
+          <t>263191</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>412827</t>
+          <t>414039</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>512243</t>
+          <t>518181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>370743</t>
+          <t>379568</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>552665</t>
+          <t>554162</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>748874</t>
+          <t>730285</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1039495</t>
+          <t>1055673</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1211284</t>
+          <t>1207790</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1566241</t>
+          <t>1563216</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>845030</t>
+          <t>870220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1223259</t>
+          <t>1225524</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>902994</t>
+          <t>889912</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1185528</t>
+          <t>1179722</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1916511</t>
+          <t>1905354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2359756</t>
+          <t>2361245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>508788</t>
+          <t>510212</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1362158</t>
+          <t>1353528</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289502</t>
+          <t>285083</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>395298</t>
+          <t>393409</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>849940</t>
+          <t>840107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1828957</t>
+          <t>1823933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>375928</t>
+          <t>395431</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>552734</t>
+          <t>551574</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>496765</t>
+          <t>492276</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1244754</t>
+          <t>1271706</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>973336</t>
+          <t>971605</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1774643</t>
+          <t>1803891</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>445121</t>
+          <t>452121</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>647721</t>
+          <t>650148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>481166</t>
+          <t>487967</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>640105</t>
+          <t>640182</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1005822</t>
+          <t>998914</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1253922</t>
+          <t>1262133</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CLASESOCIAL_Hogar_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_Hogar_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140083</t>
+          <t>140783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>182368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>383163</t>
+          <t>386126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>433187</t>
+          <t>435053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>535636</t>
+          <t>534468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>604914</t>
+          <t>608283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281025</t>
+          <t>277994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329755</t>
+          <t>331127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147602</t>
+          <t>147488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190718</t>
+          <t>193183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440208</t>
+          <t>437855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510267</t>
+          <t>508860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87246</t>
+          <t>86686</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>123899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26600</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>50969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118348</t>
+          <t>121392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165387</t>
+          <t>167713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40245</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70132</t>
+          <t>71793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72584</t>
+          <t>71052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110216</t>
+          <t>109869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85839</t>
+          <t>85771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51053</t>
+          <t>50494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88628</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127670</t>
+          <t>126618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167231</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215287</t>
+          <t>216019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>486278</t>
+          <t>482551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>548414</t>
+          <t>545703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>662456</t>
+          <t>665998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>748593</t>
+          <t>748657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383059</t>
+          <t>380200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>445646</t>
+          <t>445512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187192</t>
+          <t>187510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239267</t>
+          <t>239776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586600</t>
+          <t>583849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672168</t>
+          <t>667586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>126673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171873</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80178</t>
+          <t>79368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182699</t>
+          <t>186332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>238640</t>
+          <t>241255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74547</t>
+          <t>72976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112348</t>
+          <t>113813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>74893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159315</t>
+          <t>159971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211405</t>
+          <t>212500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99147</t>
+          <t>98904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141061</t>
+          <t>141435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>67169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101976</t>
+          <t>100823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177532</t>
+          <t>175812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233075</t>
+          <t>231328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91977</t>
+          <t>89350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131006</t>
+          <t>128935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>349043</t>
+          <t>351722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>399515</t>
+          <t>401171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450444</t>
+          <t>447787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>520473</t>
+          <t>520401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217932</t>
+          <t>216259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>268201</t>
+          <t>266594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113028</t>
+          <t>111719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152442</t>
+          <t>153280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342233</t>
+          <t>340688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407224</t>
+          <t>404616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101870</t>
+          <t>102477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>142233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120380</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164804</t>
+          <t>165392</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>72590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110877</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>82565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116785</t>
+          <t>116347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>164790</t>
+          <t>165557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215177</t>
+          <t>216750</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94830</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135177</t>
+          <t>134413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44491</t>
+          <t>44700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74485</t>
+          <t>75436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146792</t>
+          <t>150233</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>197507</t>
+          <t>199603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167509</t>
+          <t>167532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>213404</t>
+          <t>214747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>485063</t>
+          <t>486055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>546813</t>
+          <t>550613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>660939</t>
+          <t>665217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>747675</t>
+          <t>752206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251233</t>
+          <t>251293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305461</t>
+          <t>304891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>178252</t>
+          <t>176262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>227346</t>
+          <t>230666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439532</t>
+          <t>440517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514726</t>
+          <t>517794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146309</t>
+          <t>145182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192467</t>
+          <t>191514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>63382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>190763</t>
+          <t>189897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>247333</t>
+          <t>247375</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111158</t>
+          <t>110582</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152427</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123535</t>
+          <t>123472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168919</t>
+          <t>168474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>243695</t>
+          <t>246345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305611</t>
+          <t>307705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150096</t>
+          <t>148726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195982</t>
+          <t>197048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106999</t>
+          <t>106754</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148584</t>
+          <t>148618</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269361</t>
+          <t>269522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334769</t>
+          <t>333775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>599812</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>697472</t>
+          <t>695898</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1758722</t>
+          <t>1756835</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1874330</t>
+          <t>1872386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2386371</t>
+          <t>2389734</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2546137</t>
+          <t>2548391</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1177587</t>
+          <t>1182260</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1295040</t>
+          <t>1291882</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>669763</t>
+          <t>668407</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>761631</t>
+          <t>764210</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1877946</t>
+          <t>1884986</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2030559</t>
+          <t>2031048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>499735</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>586623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142595</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>194139</t>
+          <t>193396</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>664154</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>763155</t>
+          <t>763618</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>332112</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>405521</t>
+          <t>403656</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335875</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>412182</t>
+          <t>408246</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>689070</t>
+          <t>689287</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>795843</t>
+          <t>790287</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>435160</t>
+          <t>432486</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>516845</t>
+          <t>515032</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278822</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>340539</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>730490</t>
+          <t>736393</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>841847</t>
+          <t>841043</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159727</t>
+          <t>161442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207417</t>
+          <t>206401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393353</t>
+          <t>392640</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>447089</t>
+          <t>447263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>563288</t>
+          <t>566151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>642033</t>
+          <t>643209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233782</t>
+          <t>232929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283960</t>
+          <t>285834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110859</t>
+          <t>110289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152926</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353009</t>
+          <t>358680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424194</t>
+          <t>425618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118841</t>
+          <t>118697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162850</t>
+          <t>162305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41936</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71507</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170411</t>
+          <t>170375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223230</t>
+          <t>223706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77109</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77279</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119734</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49339</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81509</t>
+          <t>77508</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66901</t>
+          <t>68476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95563</t>
+          <t>94971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136591</t>
+          <t>135045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>245592</t>
+          <t>249748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305316</t>
+          <t>304787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>521806</t>
+          <t>519196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>585339</t>
+          <t>584438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>783455</t>
+          <t>780719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>874586</t>
+          <t>872563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315405</t>
+          <t>315426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>377372</t>
+          <t>377230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197336</t>
+          <t>195922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251768</t>
+          <t>249886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528703</t>
+          <t>530828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612409</t>
+          <t>612163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147408</t>
+          <t>147244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196755</t>
+          <t>194703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72612</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109730</t>
+          <t>107590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230266</t>
+          <t>228197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296195</t>
+          <t>289011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>87352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126893</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73071</t>
+          <t>73482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112387</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170123</t>
+          <t>169629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225611</t>
+          <t>228525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100643</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144392</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60228</t>
+          <t>59106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97212</t>
+          <t>95080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167471</t>
+          <t>168935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225236</t>
+          <t>221890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119362</t>
+          <t>118469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163297</t>
+          <t>161088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>373854</t>
+          <t>373807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>432267</t>
+          <t>430277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>505873</t>
+          <t>502082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>579366</t>
+          <t>579589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249730</t>
+          <t>249421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>305070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157393</t>
+          <t>158611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207321</t>
+          <t>206106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418300</t>
+          <t>422460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>496519</t>
+          <t>496597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117502</t>
+          <t>119558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164875</t>
+          <t>160864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67079</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>164481</t>
+          <t>164825</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>219516</t>
+          <t>219200</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81596</t>
+          <t>81319</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122272</t>
+          <t>121434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58186</t>
+          <t>56360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93911</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149521</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200872</t>
+          <t>204702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>77824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120553</t>
+          <t>119965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86552</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>140382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194479</t>
+          <t>194574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155944</t>
+          <t>159522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>207056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>464884</t>
+          <t>460453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>525901</t>
+          <t>525159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>635740</t>
+          <t>634868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>720619</t>
+          <t>721106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250681</t>
+          <t>249755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307550</t>
+          <t>307662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>203445</t>
+          <t>202556</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258589</t>
+          <t>256012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>463066</t>
+          <t>468094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>548495</t>
+          <t>551475</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156262</t>
+          <t>157825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204266</t>
+          <t>207487</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83445</t>
+          <t>82509</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>216332</t>
+          <t>217876</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>274647</t>
+          <t>276182</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130422</t>
+          <t>131128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179781</t>
+          <t>176565</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>118741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165987</t>
+          <t>162297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>260240</t>
+          <t>258885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>326666</t>
+          <t>320636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>133795</t>
+          <t>133657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177566</t>
+          <t>178401</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99257</t>
+          <t>98835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142261</t>
+          <t>141639</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>243850</t>
+          <t>245066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>308130</t>
+          <t>308359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>730082</t>
+          <t>727225</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>831846</t>
+          <t>826414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1802337</t>
+          <t>1816965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1927299</t>
+          <t>1934178</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2566804</t>
+          <t>2565143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2737270</t>
+          <t>2735389</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1098547</t>
+          <t>1102393</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1213518</t>
+          <t>1211433</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717585</t>
+          <t>714189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>818227</t>
+          <t>813292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1851860</t>
+          <t>1849598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2013927</t>
+          <t>2013237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>583397</t>
+          <t>585274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>675684</t>
+          <t>676652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>231269</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>292526</t>
+          <t>296691</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>831079</t>
+          <t>830943</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>953851</t>
+          <t>945163</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>379269</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>461909</t>
+          <t>465860</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>301749</t>
+          <t>300467</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>374524</t>
+          <t>375063</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>701835</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>812977</t>
+          <t>812347</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>397051</t>
+          <t>399381</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>480075</t>
+          <t>480162</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>280093</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>353175</t>
+          <t>355128</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>699548</t>
+          <t>699730</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>808753</t>
+          <t>811759</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243367</t>
+          <t>240470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293166</t>
+          <t>291255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387222</t>
+          <t>387982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>437030</t>
+          <t>436170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>644302</t>
+          <t>643843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>721227</t>
+          <t>720028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196396</t>
+          <t>195563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244489</t>
+          <t>243539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138175</t>
+          <t>137083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182930</t>
+          <t>182180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346062</t>
+          <t>346379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414294</t>
+          <t>409893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>77049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113207</t>
+          <t>114478</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102578</t>
+          <t>102393</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146833</t>
+          <t>147064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43595</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t>89822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38413</t>
+          <t>38699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65638</t>
+          <t>66763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53932</t>
+          <t>52529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75505</t>
+          <t>74249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111742</t>
+          <t>109826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265106</t>
+          <t>267297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326214</t>
+          <t>328615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>509916</t>
+          <t>506421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>573783</t>
+          <t>577625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>789881</t>
+          <t>788211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>877637</t>
+          <t>878414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319392</t>
+          <t>321257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383952</t>
+          <t>384931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226309</t>
+          <t>227621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282706</t>
+          <t>285424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560758</t>
+          <t>565313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647795</t>
+          <t>646711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130454</t>
+          <t>129261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>178181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75379</t>
+          <t>73528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>185956</t>
+          <t>182129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241627</t>
+          <t>240539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91264</t>
+          <t>87093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131577</t>
+          <t>130476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77073</t>
+          <t>79029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115391</t>
+          <t>118692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177102</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233467</t>
+          <t>232712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92783</t>
+          <t>93767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135804</t>
+          <t>136099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75047</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>113489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177648</t>
+          <t>177281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232609</t>
+          <t>234099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145416</t>
+          <t>148326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192077</t>
+          <t>196462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354018</t>
+          <t>352573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408053</t>
+          <t>408051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510846</t>
+          <t>512275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587238</t>
+          <t>587075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279545</t>
+          <t>279089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335572</t>
+          <t>335745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173102</t>
+          <t>174192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220470</t>
+          <t>223021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>465806</t>
+          <t>468424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>542218</t>
+          <t>541636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99705</t>
+          <t>100595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140716</t>
+          <t>141840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>24614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133333</t>
+          <t>128850</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>181860</t>
+          <t>176681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>61570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94733</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79675</t>
+          <t>81141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114852</t>
+          <t>117110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148502</t>
+          <t>150881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198620</t>
+          <t>199366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61750</t>
+          <t>64671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99308</t>
+          <t>98872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87753</t>
+          <t>87943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129400</t>
+          <t>129580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175844</t>
+          <t>175731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153818</t>
+          <t>155915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201195</t>
+          <t>202743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>449567</t>
+          <t>452711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>518538</t>
+          <t>518485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>619369</t>
+          <t>620959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>709759</t>
+          <t>708646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242820</t>
+          <t>241570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>295622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189008</t>
+          <t>189114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242727</t>
+          <t>244708</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>447045</t>
+          <t>447027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>525144</t>
+          <t>524289</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131779</t>
+          <t>134065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177168</t>
+          <t>180126</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60963</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>175457</t>
+          <t>173250</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>225731</t>
+          <t>230307</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>127302</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173460</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127927</t>
+          <t>126537</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174296</t>
+          <t>173661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270121</t>
+          <t>267585</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>340120</t>
+          <t>337225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161774</t>
+          <t>160426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208507</t>
+          <t>208824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123402</t>
+          <t>122893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169652</t>
+          <t>167906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>294637</t>
+          <t>292941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362048</t>
+          <t>360163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>852444</t>
+          <t>854347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>961037</t>
+          <t>958562</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1758303</t>
+          <t>1758090</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1875817</t>
+          <t>1883523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2642453</t>
+          <t>2657679</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2803331</t>
+          <t>2820917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1099546</t>
+          <t>1093665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1207276</t>
+          <t>1208147</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>775947</t>
+          <t>770458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>877477</t>
+          <t>881597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1899822</t>
+          <t>1899860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2053917</t>
+          <t>2049061</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>479151</t>
+          <t>480099</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>565326</t>
+          <t>564909</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140483</t>
+          <t>142216</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>194903</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>638827</t>
+          <t>637212</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>737815</t>
+          <t>742649</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>341358</t>
+          <t>339123</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>414341</t>
+          <t>416923</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>334751</t>
+          <t>332832</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>407293</t>
+          <t>406402</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,47 +11134,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>749500</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>693017</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>797334</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>11,53%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>749500</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>803740</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>391180</t>
+          <t>391509</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>473244</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>312589</t>
+          <t>313787</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>384354</t>
+          <t>385101</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>718318</t>
+          <t>722601</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>831543</t>
+          <t>828594</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>145440</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123318</t>
+          <t>142776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>193422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>207248</t>
+          <t>228504</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189109</t>
+          <t>209243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226411</t>
+          <t>251125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>352688</t>
+          <t>394118</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>321955</t>
+          <t>362148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381448</t>
+          <t>428203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>273468</t>
+          <t>286226</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246781</t>
+          <t>259350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303682</t>
+          <t>316354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>242284</t>
+          <t>256942</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221578</t>
+          <t>237107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262774</t>
+          <t>279255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>515751</t>
+          <t>543168</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483828</t>
+          <t>507656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553209</t>
+          <t>581272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95345</t>
+          <t>98388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77161</t>
+          <t>79614</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117903</t>
+          <t>119849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64116</t>
+          <t>69824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92785</t>
+          <t>100406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>172124</t>
+          <t>181406</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>147259</t>
+          <t>158407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>208273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>57167</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>42597</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67260</t>
+          <t>71972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>76640</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120501</t>
+          <t>133807</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102719</t>
+          <t>114919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141504</t>
+          <t>156638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>74662</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78404</t>
+          <t>94720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,27 +12141,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>76059</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58171</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83494</t>
+          <t>90578</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>131009</t>
+          <t>150721</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111384</t>
+          <t>129330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151203</t>
+          <t>177462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>627105</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>627105</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>627105</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>664968</t>
+          <t>721164</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>664968</t>
+          <t>721164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>664968</t>
+          <t>721164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1292073</t>
+          <t>1403220</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1292073</t>
+          <t>1403220</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1292073</t>
+          <t>1403220</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>144175</t>
+          <t>177760</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78328</t>
+          <t>151879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194774</t>
+          <t>205492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>227667</t>
+          <t>259364</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206156</t>
+          <t>235637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249472</t>
+          <t>284676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>371842</t>
+          <t>437124</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240425</t>
+          <t>398562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>431207</t>
+          <t>475563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>354581</t>
+          <t>380663</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197068</t>
+          <t>344726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465226</t>
+          <t>416676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>326039</t>
+          <t>367071</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301995</t>
+          <t>340194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>350490</t>
+          <t>397927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>680621</t>
+          <t>747734</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454135</t>
+          <t>704018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>783483</t>
+          <t>795924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>391432</t>
+          <t>165506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174108</t>
+          <t>139996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>751884</t>
+          <t>191253</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,17 +12597,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97026</t>
+          <t>108554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82625</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113358</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>488459</t>
+          <t>274060</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268093</t>
+          <t>244982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1070521</t>
+          <t>302536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>136556</t>
+          <t>144661</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71903</t>
+          <t>120134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186846</t>
+          <t>174738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>129545</t>
+          <t>141081</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>122264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150271</t>
+          <t>162498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>266101</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170297</t>
+          <t>253149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313239</t>
+          <t>315173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>147496</t>
+          <t>159860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77450</t>
+          <t>131817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199730</t>
+          <t>189756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>153843</t>
+          <t>168808</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135714</t>
+          <t>147894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175285</t>
+          <t>190223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>301339</t>
+          <t>328668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>204806</t>
+          <t>294095</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357757</t>
+          <t>365196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1174240</t>
+          <t>1028450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1174240</t>
+          <t>1028450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1174240</t>
+          <t>1028450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>934120</t>
+          <t>1044879</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>934120</t>
+          <t>1044879</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>934120</t>
+          <t>1044879</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2108361</t>
+          <t>2073329</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2108361</t>
+          <t>2073329</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2108361</t>
+          <t>2073329</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92057</t>
+          <t>118039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72343</t>
+          <t>97563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116027</t>
+          <t>145736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>186403</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94213</t>
+          <t>160661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>269996</t>
+          <t>204838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>278460</t>
+          <t>299982</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193455</t>
+          <t>267647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363561</t>
+          <t>332142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>230136</t>
+          <t>258775</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202079</t>
+          <t>230516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257980</t>
+          <t>294594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>238511</t>
+          <t>274270</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118175</t>
+          <t>251459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319721</t>
+          <t>301515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>468646</t>
+          <t>533044</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305947</t>
+          <t>493683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553725</t>
+          <t>569601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>133878</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98957</t>
+          <t>110718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145549</t>
+          <t>160499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68689</t>
+          <t>83747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31688</t>
+          <t>68058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>102098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>187285</t>
+          <t>217625</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120485</t>
+          <t>189461</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228415</t>
+          <t>247206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>121411</t>
+          <t>130315</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98696</t>
+          <t>105402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145417</t>
+          <t>152080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>306575</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121649</t>
+          <t>99324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>611569</t>
+          <t>136583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>427986</t>
+          <t>247718</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243080</t>
+          <t>219798</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>838746</t>
+          <t>278505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>135255</t>
+          <t>150451</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112586</t>
+          <t>125292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162499</t>
+          <t>178746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>142111</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>121815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167492</t>
+          <t>162366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>258588</t>
+          <t>292562</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169604</t>
+          <t>261828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310197</t>
+          <t>327875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>697454</t>
+          <t>791458</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>697454</t>
+          <t>791458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>697454</t>
+          <t>791458</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>923511</t>
+          <t>799473</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>923511</t>
+          <t>799473</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>923511</t>
+          <t>799473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1620964</t>
+          <t>1590931</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1620964</t>
+          <t>1590931</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1620964</t>
+          <t>1590931</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>112905</t>
+          <t>123692</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91596</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141432</t>
+          <t>149525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>258509</t>
+          <t>204654</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192971</t>
+          <t>181726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439460</t>
+          <t>231201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>371414</t>
+          <t>328346</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298749</t>
+          <t>298940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>585138</t>
+          <t>358862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257256</t>
+          <t>283471</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228487</t>
+          <t>253903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291089</t>
+          <t>314239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>283627</t>
+          <t>320164</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231336</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314431</t>
+          <t>349383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>540883</t>
+          <t>603635</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>475585</t>
+          <t>561808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590383</t>
+          <t>644728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>124976</t>
+          <t>132368</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103116</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150446</t>
+          <t>157268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108461</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85893</t>
+          <t>101905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128384</t>
+          <t>137642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>233437</t>
+          <t>251390</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198545</t>
+          <t>222162</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>267306</t>
+          <t>284317</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>182216</t>
+          <t>190089</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157250</t>
+          <t>165145</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>208682</t>
+          <t>218773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>182020</t>
+          <t>195927</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146193</t>
+          <t>174606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206665</t>
+          <t>218888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>364236</t>
+          <t>386016</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>316568</t>
+          <t>354723</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402939</t>
+          <t>422786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>236668</t>
+          <t>242621</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208554</t>
+          <t>215525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>271120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>232747</t>
+          <t>246749</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>223298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>263191</t>
+          <t>275251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>469415</t>
+          <t>489371</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>414039</t>
+          <t>454854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>518181</t>
+          <t>526563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>914021</t>
+          <t>972241</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>914021</t>
+          <t>972241</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>914021</t>
+          <t>972241</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1065365</t>
+          <t>1086516</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1065365</t>
+          <t>1086516</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1065365</t>
+          <t>1086516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1979385</t>
+          <t>2058757</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1979385</t>
+          <t>2058757</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1979385</t>
+          <t>2058757</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>494577</t>
+          <t>585105</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>379568</t>
+          <t>542644</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>554162</t>
+          <t>641534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>879827</t>
+          <t>874464</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>730285</t>
+          <t>832275</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1055673</t>
+          <t>921173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1374404</t>
+          <t>1459569</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1207790</t>
+          <t>1387677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1563216</t>
+          <t>1526740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1115441</t>
+          <t>1209135</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>870220</t>
+          <t>1142991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1225524</t>
+          <t>1269908</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1090461</t>
+          <t>1218447</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>889912</t>
+          <t>1166380</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1179722</t>
+          <t>1267957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2205902</t>
+          <t>2427582</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1905354</t>
+          <t>2342472</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2361245</t>
+          <t>2506417</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>730348</t>
+          <t>530140</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>485214</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1353528</t>
+          <t>575376</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>350956</t>
+          <t>394341</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>285083</t>
+          <t>363121</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>393409</t>
+          <t>433786</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1081304</t>
+          <t>924481</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>840107</t>
+          <t>867102</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1823933</t>
+          <t>989326</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>491612</t>
+          <t>522233</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>395431</t>
+          <t>479139</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>551574</t>
+          <t>570016</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>687211</t>
+          <t>531050</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>492276</t>
+          <t>496078</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1271706</t>
+          <t>570833</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1178824</t>
+          <t>1053283</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>971605</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1803891</t>
+          <t>1117996</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>580842</t>
+          <t>627594</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>452121</t>
+          <t>576786</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>650148</t>
+          <t>673483</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>579509</t>
+          <t>633728</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>487967</t>
+          <t>591419</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>640182</t>
+          <t>674798</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1160351</t>
+          <t>1261322</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>998914</t>
+          <t>1196218</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1262133</t>
+          <t>1331978</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3412820</t>
+          <t>3474206</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3412820</t>
+          <t>3474206</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3412820</t>
+          <t>3474206</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3587964</t>
+          <t>3652031</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3587964</t>
+          <t>3652031</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3587964</t>
+          <t>3652031</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7000784</t>
+          <t>7126237</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7000784</t>
+          <t>7126237</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7000784</t>
+          <t>7126237</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
